--- a/apps/archetest/docs/question-review/question-review-attachment.xlsx
+++ b/apps/archetest/docs/question-review/question-review-attachment.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$21</definedName>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,9 +95,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -479,211 +471,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ревью вопросов Архетеста — привязанность: 20 вопросов, две шкалы (AAX 10 + AAV 10)</t>
+          <t>Авторские вопросы Archetest — редакция v2, 2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проведено внутреннее содержательное ревью Codex; это не заключение комиссии психологов.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Этих вопросов ЕЩЁ НЕТ в тесте — ваши вердикты решают, попадут ли они туда. Срока нет.</t>
+          <t>Отчёт: prepared-batches-review-2026-10-16.md и JSON с исходниками, ключами и замечаниями.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Пакеты включены в рабочий банк для пилота. Интервью и эмпирическая валидация не проведены.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Что строим:</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Период: последние шесть месяцев; варианты: никогда / редко / часто / почти каждый раз.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Прототип — ECR-R (Fraley, Waller &amp; Brennan, 2000) и ECR-RS (Fraley et al., 2011), только на</t>
+          <t>Нет подходящих ситуаций или трудно ответить — пропуск, а не нулевой балл.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>уровне конструкта: пункты ECR-R не переводятся и не перефразируются. Два независимых измерения:</t>
+          <t>СДВГ: обычные условия с привычной поддержкой; 9 областей INA и 9 HYI; это не ASRS.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>• AAX «Тревога в привязанности» — страх быть покинутым, потребность в подтверждениях,</t>
+          <t>Привязанность: одни выбранные безопасные близкие отношения; без вывода о стиле.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  гипербдительность к сигналам охлаждения.</t>
+          <t>HON: честность–скромность, четыре фасета; не Agreeableness и не тест нравственности.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>• AAV «Избегание близости» — дискомфорт от откровенности и зависимости, дистанция при сближении.</t>
+          <t>HON имеет обратный ключ 3/2/1/0; остальные новые пункты — прямой 0/1/2/3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Низкие оба — надёжный стиль; психолог в кабинете увидит квадрант, а не типологический ярлык.</t>
+          <t>Стратегии помощи, вежливость, экономия и разумные границы сами по себе не дают баллов.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Главный вопрос ревью — не продублировали ли мы шкалы ядра:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>• AAX ↔ BOR (страх покинутости) и DEP (потребность в опеке). Разводим: без импульсивности и</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  качелей идеализации, не про беспомощность в решениях — только тревога о связи.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• AAV ↔ SZD (безразличие к связям) и AVD (страх оценки). Разводим: все сюжеты — внутри УЖЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  близких отношений (партнёр, близкий друг), не знакомства и не чужие люди.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Отметьте вопросы, которые, на ваш взгляд, меряют BOR/DEP/SZD/AVD, а не привязанность.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Коротко по таблице:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>• Колонка «Шкала» показывает грань измерения, «Код» — AAX или AAV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>• Варианты скорят ТОЛЬКО AAX/AAV (один вариант в AAX-вопросе даёт AAV 1 — это намеренно).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ни одного балла шкалам ядра. Пустые скобки = дистрактор.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>• «Обр.» = да — балл набирается вариантом со спокойным, даже зрелым фасадом, за которым стратегия:</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  «делаю вид, что мне всё равно, а сам(а) прислушиваюсь», «предлагаю каждому всё обдумать — и</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  не возвращаюсь к разговору». Проверьте, честна ли инверсия и не наказывает ли она здоровую паузу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>• «Вердикт»: ОК / Править / Удалить. «Комментарий / правка» — формулировку можно прямо в ячейке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>Что ещё важно:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>1. Социальная желательность: «надёжный» вариант часто виден. Где он слишком очевиден — отметьте.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>2. Гендер: в RU где нужно «он(а)», в EN — they. Нет ли сценариев, которые читаются только для пары</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   одного типа?</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>3. Язык и этика — те же критерии, что для 5.1 (INSTRUCTIONS.md).</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Следующий этап: реальные когнитивные интервью и проверка измерительных свойств.</t>
         </is>
       </c>
     </row>
@@ -777,7 +642,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Чувствительность к сигналам</t>
+          <t>Сигналы охлаждения</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -788,35 +653,43 @@
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Партнёр весь вечер отвечает на ваши сообщения коротко и без смайликов.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто после непривычно короткого сообщения близкого человека вы долго тревожитесь, что его чувства к вам изменились? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Начинаю перебирать, что сделал(а) не так, и не могу успокоиться, пока не спрошу
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[AAX 1]</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Наверное, устал(а) или занят(а) — поговорим, когда увидимся
-[]</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Тоже отвечаю коротко
-[]</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>Пишу «Всё в порядке?» — и дальше не переживаю
-[AAX 1]</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -824,7 +697,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Потребность в подтверждении</t>
+          <t>Подтверждение связи</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -835,35 +708,43 @@
       <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Близкий человек редко говорит о чувствах словами — зато заботится делами.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто получив искреннее подтверждение тёплых чувств, вы вскоре снова нуждаетесь в нём, чтобы не сомневаться в отношениях? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Дела для меня важнее слов
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Иногда прошу сказать это вслух — и мне достаточно
+          <t>Редко
 [AAX 1]</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Мне этого мало: без слов я то и дело сомневаюсь, что меня ещё любят
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Сам(а) тоже не любитель говорить о чувствах
-[]</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -882,35 +763,43 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Партнёр на неделю уходит в поход в горы — связи там почти не будет.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто во время заранее согласованной разлуки вы тревожитесь именно о том, что близкий человек перестанет нуждаться в отношениях с вами? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Всё в порядке: отдохну и займусь своими делами
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Первые дни скучаю, потом втягиваюсь
-[]</t>
+          <t>Редко
+[AAX 1]</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Прошу выходить на связь при любой возможности — без вестей места себе не нахожу
+          <t>Часто
 [AAX 2]</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Всю неделю внутри тревожно: вдруг там, без меня, он(а) поймёт, что так даже лучше
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -918,7 +807,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Протестное поведение</t>
+          <t>Пауза после разногласия</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -926,42 +815,46 @@
           <t>AAX</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>После ссоры партнёр ушёл в другую комнату и молчит уже час.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто пока близкий человек берёт согласованную паузу после спора, вы воспринимаете это как угрозу вашим отношениям? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Иду мириться первым(ой) — не хочу, чтобы ссора остывала в тишине
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Делаю вид, что мне всё равно, но прислушиваюсь к каждому звуку из-за двери
+          <t>Редко
+[AAX 1]</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Даю время остыть — вернёмся к разговору позже
-[]</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>Занимаюсь своими делами — так мне даже спокойнее
-[AAV 1]</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -969,7 +862,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Самоценность через отношения</t>
+          <t>Значимость для другого</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -980,35 +873,43 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Близкий человек не спросил, как прошёл ваш важный день, хотя вы говорили о нём всю неделю.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто если близкий человек забыл спросить о важном для вас событии, вы начинаете сомневаться, дороги ли вы ему? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Рассказываю сам(а) — наверное, просто забыл(а)
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Кажется, я для этого человека не так уж важен(на), — и от этого тяжело
+          <t>Редко
+[AAX 1]</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Немного обидно, но не придаю значения
-[]</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Жду, вспомнит ли сам(а), — и с каждым часом тревожнее
-[AAX 2]</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1016,7 +917,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Гипербдительность</t>
+          <t>Проверки связи</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1024,42 +925,46 @@
           <t>AAX</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Партнёр говорит, что вечером задержится с коллегами.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто когда близкий человек занят своими делами, вы снова и снова проверяете его доступность, чтобы убедиться, что связь между вами сохраняется? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Хорошо, проведу вечер по-своему
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Прошу написать, когда поедет домой
-[]</t>
+          <t>Редко
+[AAX 1]</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Расстраиваюсь и говорю об этом прямо
-[AAX 1]</t>
+          <t>Часто
+[AAX 2]</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Говорю «конечно, хорошо тебе провести время», а потом весь вечер проверяю, когда он(а) был(а) в сети
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1067,7 +972,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Страх покинутости</t>
+          <t>Отдельное время</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1078,35 +983,43 @@
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Партнёр говорит: «Мне нужно побыть наедине с собой в эти выходные».</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто просьба близкого человека провести время отдельно вызывает у вас страх, что он хочет закончить отношения? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Понимаю — мне это тоже бывает нужно
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Внутри всё обрывается: кажется, это начало конца
+          <t>Редко
+[AAX 1]</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Немного обидно, но переживу
-[AAX 1]</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Отлично, у меня как раз свои планы
-[]</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1114,7 +1027,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Сравнение</t>
+          <t>Сравнение отношений</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1122,42 +1035,46 @@
           <t>AAX</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Партнёр с теплотой вспоминает, как весело было в студенческой компании — ещё до знакомства с вами.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто слыша о других дорогих близкому человеку людях, вы долго тревожитесь, что ваши отношения для него менее важны? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Улыбаюсь и киваю, а потом весь вечер прокручиваю, не было ли ему(ей) тогда лучше, чем сейчас со мной
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[AAX 1]</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Спрашиваю полушутя: «А сейчас скучно?»
-[AAX 1]</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>С интересом слушаю — хорошие были времена
-[]</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>Рассказываю в ответ свои студенческие истории
-[]</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1165,7 +1082,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Тревога в затишье</t>
+          <t>Спокойный период</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1176,35 +1093,43 @@
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>В отношениях уже месяц всё ровно: без ссор, но и без особых событий.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто в спокойный период отношений вы ищете признаки охлаждения, хотя конкретных поводов для этого не замечаете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Хорошо — спокойствие и значит, что всё в порядке
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Предлагаю что-то новое — поездку, общее дело
-[]</t>
+          <t>Редко
+[AAX 1]</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Становится тревожно: затишье кажется подозрительным, хочется проверить, что чувства на месте
+          <t>Часто
+[AAX 2]</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Скучновато, но это нормально
-[]</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1212,7 +1137,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Страх разочаровать</t>
+          <t>Сдержанная реакция</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1220,42 +1145,46 @@
           <t>AAX</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Вы сделали близкому человеку приятное, а благодарность прозвучала сдержанно.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто сдержанная благодарность близкого человека заставляет вас долго сомневаться в его расположении к вам? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Мне не нужны бурные реакции — главное, что порадовал(а)
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Спрашиваю, понравилось ли на самом деле
+          <t>Редко
 [AAX 1]</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>В следующий раз придумаю что-то другое
-[]</t>
+          <t>Часто
+[AAX 2]</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Говорю себе, что это неважно, но потом ещё долго гадаю, не разочаровал(а) ли
+          <t>Почти каждый раз
 [AAX 3]</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1274,35 +1203,43 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Партнёр просит рассказать, что вас на самом деле тревожит последнее время.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вам хочется поделиться важным переживанием с близким человеком, но вы закрываетесь именно потому, что откровенность делает вас слишком уязвимыми? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Рассказываю — с близким можно
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Отшучиваюсь или говорю «всё нормально» — делиться таким мне неуютно
+          <t>Редко
+[AAV 1]</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Рассказываю частично, самое личное оставляю при себе
-[AAV 1]</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Расскажу, когда сам(а) созрею, — пока нет
-[]</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1310,7 +1247,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Опора на себя</t>
+          <t>Принятие помощи</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1321,35 +1258,43 @@
       <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Вы несколько дней лежите с температурой, и близкий человек предлагает приехать и помочь.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы отказываетесь от нужной и удобной помощи близкого человека именно потому, что не хотите на него полагаться? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>С радостью соглашаюсь
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Прошу только привезти лекарства
-[]</t>
+          <t>Редко
+[AAV 1]</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, хотя мне неловко
-[AAV 1]</t>
+          <t>Часто
+[AAV 2]</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Отказываюсь: справлюсь сам(а), не люблю быть обузой и чувствовать себя обязанным(ой)
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1357,7 +1302,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Дистанция при сближении</t>
+          <t>Сближение</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1368,35 +1313,43 @@
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Отношения развиваются хорошо, и партнёр предлагает съехаться.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто при желанном для обоих сближении вам хочется отдалиться именно из-за возрастающей эмоциональной близости? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Радуюсь — давно этого хотел(а)
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Обсуждаем, как будем делить пространство и быт
-[]</t>
+          <t>Редко
+[AAV 1]</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Чем серьёзнее всё становится, тем сильнее хочется притормозить и отступить
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Соглашаюсь, но выговариваю себе отдельную комнату
-[AAV 1]</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1404,7 +1357,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Эмоциональная сдержанность</t>
+          <t>Поддержка другого</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1412,42 +1365,46 @@
           <t>AAV</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Партнёр плачет после тяжёлого разговора с родителями.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы уходите от эмоционального разговора с близким человеком именно потому, что вам трудно выдерживать такую близость? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Обнимаю и просто побуду рядом
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Предлагаю дельные решения — так от меня больше пользы, чем от объятий
+          <t>Редко
+[AAV 1]</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Мне неловко, хочется выйти из комнаты
-[AAV 2]</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Спрашиваю, чем могу помочь
-[]</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1455,7 +1412,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Личное пространство</t>
+          <t>Совместное время</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1466,35 +1423,43 @@
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Партнёр хочет проводить вместе все выходные подряд.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто даже при удобном для вас количестве совместного времени вы чувствуете желание отдалиться, когда общение становится особенно тёплым? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Здорово, мне тоже этого хочется
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Договариваемся: день вместе, день каждый по-своему
-[]</t>
+          <t>Редко
+[AAV 1]</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Через пару дней вместе начинаю задыхаться и ищу повод побыть в одиночестве
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Соглашаюсь, но заранее придумываю себе дела
-[AAV 2]</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1502,7 +1467,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Разговоры о будущем</t>
+          <t>Общее будущее</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1510,42 +1475,46 @@
           <t>AAV</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Партнёр заводит разговор о планах на пять лет вперёд: дети, ипотека, переезд.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы избегаете разговора о желанных для вас обоих общих планах именно потому, что он усиливает ощущение близости? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>С интересом обсуждаю
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Честно говорю, что пока не готов(а) к таким планам
+          <t>Редко
 [AAV 1]</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Предлагаю вернуться к этому, когда прояснится с работой
-[]</t>
+          <t>Часто
+[AAV 2]</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Говорю, что загадывать так далеко бессмысленно, — хотя на самом деле от таких разговоров мне просто не по себе
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1553,7 +1522,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Неприятие зависимости</t>
+          <t>Взаимная опора</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1564,35 +1533,43 @@
       <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Близкий человек всё чаще советуется с вами по любому поводу и явно на вас опирается.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто готовность близкого человека опираться на вас в разумных пределах вызывает желание уменьшить эмоциональную близость? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Мне приятно быть опорой
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Меня это напрягает: не люблю, когда от меня так зависят
+          <t>Редко
+[AAV 1]</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Поддерживаю, но мягко подталкиваю к самостоятельности
-[]</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>Помогаю, но начинаю отвечать всё реже
-[AAV 2]</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1600,7 +1577,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Уход от выяснения</t>
+          <t>Обсуждение отношений</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1608,42 +1585,46 @@
           <t>AAV</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Партнёр хочет обсудить то, что давно назревало в отношениях.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы откладываете безопасный и спокойный разговор об отношениях, потому что не хотите раскрывать близкому человеку свои чувства? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь: давно пора
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Предлагаю сначала каждому спокойно всё обдумать — и потом так и не возвращаюсь к разговору
+          <t>Редко
+[AAV 1]</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Ухожу от темы и переключаюсь на дела
-[AAV 2]</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>Прошу назначить время, чтобы подготовиться
-[]</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1651,7 +1632,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Телесная близость</t>
+          <t>Выражение нежности</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1662,35 +1643,43 @@
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Партнёр любит держаться за руки и обниматься на людях.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы сдерживаете желанное для вас проявление нежности наедине, потому что ощущаете себя слишком открытыми перед близким человеком? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Мне это тоже нравится
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Нравится, но не на людях
-[]</t>
+          <t>Редко
+[AAV 1]</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Мягко высвобождаюсь и перевожу всё в шутку
+          <t>Часто
 [AAV 2]</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Терплю, но внутренне сжимаюсь — слишком много близости
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1698,7 +1687,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Самодостаточность</t>
+          <t>Сокрытие трудностей</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1706,48 +1695,52 @@
           <t>AAV</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>На работе трудный период, и вечером близкий человек спрашивает, как у вас дела.</t>
+          <t>Вспомните одни безопасные близкие отношения, в которых вы хотите сохранять связь, и отвечайте о них. За последние шесть месяцев как часто вы скрываете от близкого человека переживания, которыми хотели бы поделиться, чтобы не оказаться эмоционально зависимыми? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Рассказываю — мне становится легче
+          <t>Никогда или почти никогда
 []</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Говорю, что справляюсь, — и справляюсь; зачем грузить близких
+          <t>Редко
+[AAV 1]</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[AAV 2]</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [AAV 3]</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Жалуюсь от души
-[]</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Рассказываю, но только когда всё уже решено
-[AAV 2]</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K21"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править или Удалить" type="list">
-      <formula1>"ОК,Править,Удалить"</formula1>
+    <dataValidation sqref="J2:J21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править, Удалить или Для пилота" type="list">
+      <formula1>"ОК,Править,Удалить,Для пилота"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
